--- a/output/admin-reporting/payments-KHR.xlsx
+++ b/output/admin-reporting/payments-KHR.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
